--- a/wxdgaming.boot2.starter.excel/src/main/resources/范例.xlsx
+++ b/wxdgaming.boot2.starter.excel/src/main/resources/范例.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="q_itemshop_vip" sheetId="4" r:id="rId1"/>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>vip礼包</t>
   </si>
@@ -211,9 +211,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>wxdgaming.boot2.core.timer.CronExpress</t>
   </si>
   <si>
     <t>bool</t>
@@ -464,12 +461,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -972,10 +969,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1336,7 +1333,7 @@
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1413,7 +1410,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:12">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -1430,65 +1427,65 @@
         <v>15</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:12">
       <c r="A6" s="6">
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="8" t="b">
         <v>1</v>
@@ -1496,28 +1493,28 @@
       <c r="H6" s="6">
         <v>1</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>34</v>
+      <c r="I6" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:12">
       <c r="A7" s="6">
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" s="6">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="8" t="b">
         <v>0</v>
@@ -1525,28 +1522,28 @@
       <c r="H7" s="6">
         <v>1</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>37</v>
+      <c r="I7" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:12">
       <c r="A8" s="6">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" s="6">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="8" t="b">
         <v>1</v>
@@ -1554,8 +1551,8 @@
       <c r="H8" s="6">
         <v>1</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>40</v>
+      <c r="I8" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
